--- a/PowGen2050.xlsx
+++ b/PowGen2050.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="46">
   <si>
     <t xml:space="preserve">Power Generation</t>
   </si>
@@ -147,6 +147,18 @@
   </si>
   <si>
     <t xml:space="preserve">Solar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tgn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fosil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fosiln</t>
   </si>
 </sst>
 </file>
@@ -337,10 +349,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z19"/>
-  <sheetFormatPr defaultColWidth="10.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="10.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="7" style="0" width="12.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="0" width="10.85"/>
@@ -1529,8 +1541,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:G26"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B2:K52"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="0" t="s">
@@ -1540,15 +1552,27 @@
         <v>37</v>
       </c>
       <c r="D2" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="F2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="G2" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="I2" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="0" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1557,11 +1581,11 @@
         <v>5</v>
       </c>
       <c r="C3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="0" t="n">
         <v>-2.42835265784613E-013</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E3" s="0" t="n">
         <v>0</v>
       </c>
@@ -1569,6 +1593,20 @@
         <v>0</v>
       </c>
       <c r="G3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <f aca="false">C3+F3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <f aca="false">D3+E3+G3+H3</f>
+        <v>-2.42835265784613E-013</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1577,11 +1615,11 @@
         <v>6</v>
       </c>
       <c r="C4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="0" t="n">
         <v>-6.821279652236E-014</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E4" s="0" t="n">
         <v>0</v>
       </c>
@@ -1589,6 +1627,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <f aca="false">C4+F4</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <f aca="false">D4+E4+G4+H4</f>
+        <v>-6.821279652236E-014</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1597,18 +1649,32 @@
         <v>7</v>
       </c>
       <c r="C5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="0" t="n">
         <v>-0.0205237282270164</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="0" t="n">
         <v>-0.000163971139298155</v>
       </c>
-      <c r="F5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="0" t="n">
+      <c r="H5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <f aca="false">C5+F5</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <f aca="false">D5+E5+G5+H5</f>
+        <v>-0.0206876993663146</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1617,18 +1683,32 @@
         <v>8</v>
       </c>
       <c r="C6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="0" t="n">
         <v>-77.2923605033224</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="0" t="n">
         <v>-0.617515310592598</v>
       </c>
-      <c r="F6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="0" t="n">
+      <c r="H6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <f aca="false">C6+F6</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <f aca="false">D6+E6+G6+H6</f>
+        <v>-77.909875813915</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1637,18 +1717,32 @@
         <v>9</v>
       </c>
       <c r="C7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="0" t="n">
         <v>-170.841637216676</v>
       </c>
-      <c r="D7" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="0" t="n">
         <v>-3.40633644775633</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="H7" s="0" t="n">
         <v>-255.518292973451</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="I7" s="0" t="n">
+        <f aca="false">C7+F7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <f aca="false">D7+E7+G7+H7</f>
+        <v>-429.766266637883</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1657,18 +1751,32 @@
         <v>10</v>
       </c>
       <c r="C8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="0" t="n">
         <v>-220.638622250211</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="E8" s="0" t="n">
         <v>-17.3704065421798</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="F8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="0" t="n">
         <v>-38.926562839603</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="H8" s="0" t="n">
         <v>-322.549621917463</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="I8" s="0" t="n">
+        <f aca="false">C8+F8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <f aca="false">D8+E8+G8+H8</f>
+        <v>-599.485213549457</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>-10.4996829079378</v>
       </c>
     </row>
@@ -1677,18 +1785,32 @@
         <v>11</v>
       </c>
       <c r="C9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="0" t="n">
         <v>-178.806368605168</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="E9" s="0" t="n">
         <v>-27.381437784952</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="F9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="0" t="n">
         <v>-38.9969615526643</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="H9" s="0" t="n">
         <v>-373.68210260979</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="I9" s="0" t="n">
+        <f aca="false">C9+F9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <f aca="false">D9+E9+G9+H9</f>
+        <v>-618.866870552574</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1697,18 +1819,32 @@
         <v>12</v>
       </c>
       <c r="C10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="0" t="n">
         <v>-106.369069351925</v>
       </c>
-      <c r="D10" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0" t="n">
         <v>-3.83074819467528</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="H10" s="0" t="n">
         <v>-373.113083367753</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="I10" s="0" t="n">
+        <f aca="false">C10+F10</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <f aca="false">D10+E10+G10+H10</f>
+        <v>-483.312900914353</v>
+      </c>
+      <c r="K10" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1717,18 +1853,32 @@
         <v>13</v>
       </c>
       <c r="C11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="0" t="n">
         <v>-151.437776710124</v>
       </c>
-      <c r="D11" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="0" t="n">
         <v>-1.20988859845448</v>
       </c>
-      <c r="F11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="0" t="n">
+      <c r="H11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <f aca="false">C11+F11</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <f aca="false">D11+E11+G11+H11</f>
+        <v>-152.647665308579</v>
+      </c>
+      <c r="K11" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1737,18 +1887,32 @@
         <v>14</v>
       </c>
       <c r="C12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="0" t="n">
         <v>-0.198423404499578</v>
       </c>
-      <c r="D12" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="0" t="n">
         <v>-0.00158527297472028</v>
       </c>
-      <c r="F12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="0" t="n">
+      <c r="H12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <f aca="false">C12+F12</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="0" t="n">
+        <f aca="false">D12+E12+G12+H12</f>
+        <v>-0.200008677474298</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1757,18 +1921,32 @@
         <v>15</v>
       </c>
       <c r="C13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="0" t="n">
         <v>-0.0273376059980756</v>
       </c>
-      <c r="D13" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="0" t="n">
         <v>-0.000218409557543055</v>
       </c>
-      <c r="F13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="0" t="n">
+      <c r="H13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="0" t="n">
+        <f aca="false">C13+F13</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="0" t="n">
+        <f aca="false">D13+E13+G13+H13</f>
+        <v>-0.0275560155556187</v>
+      </c>
+      <c r="K13" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1777,11 +1955,11 @@
         <v>16</v>
       </c>
       <c r="C14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="0" t="n">
         <v>-2.72698530423554E-015</v>
       </c>
-      <c r="D14" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E14" s="0" t="n">
         <v>0</v>
       </c>
@@ -1789,6 +1967,20 @@
         <v>0</v>
       </c>
       <c r="G14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="0" t="n">
+        <f aca="false">C14+F14</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="0" t="n">
+        <f aca="false">D14+E14+G14+H14</f>
+        <v>-2.72698530423554E-015</v>
+      </c>
+      <c r="K14" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1811,6 +2003,20 @@
       <c r="G15" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="H15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="0" t="n">
+        <f aca="false">C15+F15</f>
+        <v>1.89626092605977E-013</v>
+      </c>
+      <c r="J15" s="0" t="n">
+        <f aca="false">D15+E15+G15+H15</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
@@ -1831,24 +2037,52 @@
       <c r="G16" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="H16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="0" t="n">
+        <f aca="false">C16+F16</f>
+        <v>2.47836473565854E-013</v>
+      </c>
+      <c r="J16" s="0" t="n">
+        <f aca="false">D16+E16+G16+H16</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="0" t="n">
         <v>-0.257293621189743</v>
       </c>
-      <c r="D17" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="0" t="n">
         <v>-0.00205560742831767</v>
       </c>
-      <c r="F17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="0" t="n">
+      <c r="H17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="0" t="n">
+        <f aca="false">C17+F17</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="0" t="n">
+        <f aca="false">D17+E17+G17+H17</f>
+        <v>-0.259349228618061</v>
+      </c>
+      <c r="K17" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1857,18 +2091,32 @@
         <v>20</v>
       </c>
       <c r="C18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="0" t="n">
         <v>-78.8287713035937</v>
       </c>
-      <c r="D18" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="0" t="n">
         <v>-0.780104019179287</v>
       </c>
-      <c r="F18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="0" t="n">
+      <c r="H18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <f aca="false">C18+F18</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="0" t="n">
+        <f aca="false">D18+E18+G18+H18</f>
+        <v>-79.608875322773</v>
+      </c>
+      <c r="K18" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1877,18 +2125,32 @@
         <v>21</v>
       </c>
       <c r="C19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="0" t="n">
         <v>-168.723363434397</v>
       </c>
-      <c r="D19" s="0" t="n">
+      <c r="E19" s="0" t="n">
         <v>-2.847526</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="F19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="0" t="n">
         <v>-37.4673483365772</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="H19" s="0" t="n">
         <v>-225.633482370798</v>
       </c>
-      <c r="G19" s="0" t="n">
+      <c r="I19" s="0" t="n">
+        <f aca="false">C19+F19</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="0" t="n">
+        <f aca="false">D19+E19+G19+H19</f>
+        <v>-434.671720141772</v>
+      </c>
+      <c r="K19" s="0" t="n">
         <v>-0.268881626136441</v>
       </c>
     </row>
@@ -1897,18 +2159,32 @@
         <v>22</v>
       </c>
       <c r="C20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="0" t="n">
         <v>-235.745176925154</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="E20" s="0" t="n">
         <v>-2.8955875</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="F20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="0" t="n">
         <v>-8.32892317342953</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="H20" s="0" t="n">
         <v>-164.83844936318</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="I20" s="0" t="n">
+        <f aca="false">C20+F20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <f aca="false">D20+E20+G20+H20</f>
+        <v>-411.808136961764</v>
+      </c>
+      <c r="K20" s="0" t="n">
         <v>-195.863761918054</v>
       </c>
     </row>
@@ -1917,18 +2193,32 @@
         <v>23</v>
       </c>
       <c r="C21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="0" t="n">
         <v>-197.546340799196</v>
       </c>
-      <c r="D21" s="0" t="n">
+      <c r="E21" s="0" t="n">
         <v>-19.294746335</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="F21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="0" t="n">
         <v>-28.0200421516702</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="H21" s="0" t="n">
         <v>-188.194246802403</v>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="I21" s="0" t="n">
+        <f aca="false">C21+F21</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <f aca="false">D21+E21+G21+H21</f>
+        <v>-433.055376088269</v>
+      </c>
+      <c r="K21" s="0" t="n">
         <v>-149.229719130444</v>
       </c>
     </row>
@@ -1937,18 +2227,32 @@
         <v>24</v>
       </c>
       <c r="C22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="0" t="n">
         <v>-180.384175981003</v>
       </c>
-      <c r="D22" s="0" t="n">
+      <c r="E22" s="0" t="n">
         <v>-2.91852825</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="F22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="0" t="n">
         <v>-26.0384421559375</v>
       </c>
-      <c r="F22" s="0" t="n">
+      <c r="H22" s="0" t="n">
         <v>-202.25962868506</v>
       </c>
-      <c r="G22" s="0" t="n">
+      <c r="I22" s="0" t="n">
+        <f aca="false">C22+F22</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <f aca="false">D22+E22+G22+H22</f>
+        <v>-411.600775072001</v>
+      </c>
+      <c r="K22" s="0" t="n">
         <v>-53.392538964457</v>
       </c>
     </row>
@@ -1957,18 +2261,32 @@
         <v>25</v>
       </c>
       <c r="C23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="0" t="n">
         <v>-76.3455680370673</v>
       </c>
-      <c r="D23" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="0" t="n">
         <v>-1.44630418373597</v>
       </c>
-      <c r="F23" s="0" t="n">
+      <c r="H23" s="0" t="n">
         <v>-99.6120699441572</v>
       </c>
-      <c r="G23" s="0" t="n">
+      <c r="I23" s="0" t="n">
+        <f aca="false">C23+F23</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <f aca="false">D23+E23+G23+H23</f>
+        <v>-177.403942164961</v>
+      </c>
+      <c r="K23" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1977,18 +2295,32 @@
         <v>26</v>
       </c>
       <c r="C24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="0" t="n">
         <v>-2.57097366148278</v>
       </c>
-      <c r="D24" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="0" t="n">
         <v>-0.0407834380693457</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="H24" s="0" t="n">
         <v>-2.5337551504983</v>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="I24" s="0" t="n">
+        <f aca="false">C24+F24</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <f aca="false">D24+E24+G24+H24</f>
+        <v>-5.14551225005043</v>
+      </c>
+      <c r="K24" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2003,12 +2335,26 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="0" t="n">
         <v>0.0309452274086725</v>
       </c>
-      <c r="F25" s="0" t="n">
+      <c r="G25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="0" t="n">
         <v>-0.0713946185977547</v>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="I25" s="0" t="n">
+        <f aca="false">C25+F25</f>
+        <v>0.0713946185978425</v>
+      </c>
+      <c r="J25" s="0" t="n">
+        <f aca="false">D25+E25+G25+H25</f>
+        <v>-0.0713946185977547</v>
+      </c>
+      <c r="K25" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2017,11 +2363,11 @@
         <v>28</v>
       </c>
       <c r="C26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="0" t="n">
         <v>-2.20552742735691E-013</v>
       </c>
-      <c r="D26" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="E26" s="0" t="n">
         <v>0</v>
       </c>
@@ -2029,6 +2375,370 @@
         <v>0</v>
       </c>
       <c r="G26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <f aca="false">C26+F26</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="0" t="n">
+        <f aca="false">D26+E26+G26+H26</f>
+        <v>-2.20552742735691E-013</v>
+      </c>
+      <c r="K26" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F28" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="I28" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F29" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="0" t="n">
+        <v>-2.42835265784613E-013</v>
+      </c>
+      <c r="I29" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F30" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="G30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="0" t="n">
+        <v>-6.821279652236E-014</v>
+      </c>
+      <c r="I30" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F31" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="0" t="n">
+        <v>-0.0206876993663146</v>
+      </c>
+      <c r="I31" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F32" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="0" t="n">
+        <v>-77.909875813915</v>
+      </c>
+      <c r="I32" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F33" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="0" t="n">
+        <v>-429.766266637883</v>
+      </c>
+      <c r="I33" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F34" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="0" t="n">
+        <v>-599.485213549457</v>
+      </c>
+      <c r="I34" s="0" t="n">
+        <v>-10.4996829079378</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F35" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="0" t="n">
+        <v>-618.866870552574</v>
+      </c>
+      <c r="I35" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F36" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="0" t="n">
+        <v>-483.312900914353</v>
+      </c>
+      <c r="I36" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F37" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="0" t="n">
+        <v>-152.647665308579</v>
+      </c>
+      <c r="I37" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F38" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="0" t="n">
+        <v>-0.200008677474298</v>
+      </c>
+      <c r="I38" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F39" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="0" t="n">
+        <v>-0.0275560155556187</v>
+      </c>
+      <c r="I39" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F40" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="0" t="n">
+        <v>-2.72698530423554E-015</v>
+      </c>
+      <c r="I40" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F41" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>1.89626092605977E-013</v>
+      </c>
+      <c r="H41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F42" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>2.47836473565854E-013</v>
+      </c>
+      <c r="H42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F43" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="0" t="n">
+        <v>-0.259349228618061</v>
+      </c>
+      <c r="I43" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F44" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>-79.608875322773</v>
+      </c>
+      <c r="I44" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F45" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="0" t="n">
+        <v>-434.671720141772</v>
+      </c>
+      <c r="I45" s="0" t="n">
+        <v>-0.268881626136441</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F46" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="0" t="n">
+        <v>-411.808136961764</v>
+      </c>
+      <c r="I46" s="0" t="n">
+        <v>-195.863761918054</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F47" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="0" t="n">
+        <v>-433.055376088269</v>
+      </c>
+      <c r="I47" s="0" t="n">
+        <v>-149.229719130444</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F48" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="0" t="n">
+        <v>-411.600775072001</v>
+      </c>
+      <c r="I48" s="0" t="n">
+        <v>-53.392538964457</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F49" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="0" t="n">
+        <v>-177.403942164961</v>
+      </c>
+      <c r="I49" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F50" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="0" t="n">
+        <v>-5.14551225005043</v>
+      </c>
+      <c r="I50" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F51" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="G51" s="0" t="n">
+        <v>0.0713946185978425</v>
+      </c>
+      <c r="H51" s="0" t="n">
+        <v>-0.0713946185977547</v>
+      </c>
+      <c r="I51" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F52" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="0" t="n">
+        <v>-2.20552742735691E-013</v>
+      </c>
+      <c r="I52" s="0" t="n">
         <v>0</v>
       </c>
     </row>
